--- a/server/excel/release/cyclic-event-2.xlsx
+++ b/server/excel/release/cyclic-event-2.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="全服限购活动" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="全服限购活动商品" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="全服限购活动次数奖励" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="锦鲤活动" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="锦鲤活动奖励" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="砸金蛋活动" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="砸金蛋方式" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="砸金蛋奖励" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="兽魂周卡活动" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="兽魂周卡档位" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="图腾周卡活动" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="图腾周卡档位" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="召唤福利基础" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="召唤福利奖励" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Sheet1" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全服限购活动" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全服限购活动商品" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全服限购活动次数奖励" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锦鲤活动" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="锦鲤活动奖励" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="砸金蛋活动" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="砸金蛋方式" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="砸金蛋奖励" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="兽魂周卡活动" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="兽魂周卡档位" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图腾周卡活动" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图腾周卡档位" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="召唤福利基础" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="召唤福利奖励" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="352">
   <si>
     <t xml:space="preserve">活动ID</t>
   </si>
@@ -964,6 +964,9 @@
     <t xml:space="preserve">0:1:1000000#3:500015:500#3:100342:30000#3:500093:150</t>
   </si>
   <si>
+    <t xml:space="preserve">Thẻ tuần Đồ đằng</t>
+  </si>
+  <si>
     <t xml:space="preserve">图腾周卡</t>
   </si>
   <si>
@@ -979,10 +982,10 @@
     <t xml:space="preserve">功能ID</t>
   </si>
   <si>
-    <t xml:space="preserve">召唤福利</t>
-  </si>
-  <si>
-    <t xml:space="preserve">解签福利</t>
+    <t xml:space="preserve">Phúc lợi triệu hồi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phúc lợi giải quẻ</t>
   </si>
   <si>
     <t xml:space="preserve">轮次</t>
@@ -1767,7 +1770,7 @@
         <v>10002</v>
       </c>
       <c r="B3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1790,7 +1793,7 @@
         <v>10003</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1813,7 +1816,7 @@
         <v>10004</v>
       </c>
       <c r="B5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1882,13 +1885,13 @@
         <v>1000000</v>
       </c>
       <c r="C2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F2" t="s">
         <v>309</v>
@@ -1940,10 +1943,10 @@
         <v>81</v>
       </c>
       <c r="H1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2">
@@ -1951,7 +1954,7 @@
         <v>10001</v>
       </c>
       <c r="B2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1980,7 +1983,7 @@
         <v>10002</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -2029,13 +2032,13 @@
         <v>51</v>
       </c>
       <c r="D1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E1" t="s">
         <v>22</v>
       </c>
       <c r="F1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2">
@@ -2046,7 +2049,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -2114,7 +2117,7 @@
         <v>500</v>
       </c>
       <c r="C6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -2131,7 +2134,7 @@
         <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -2199,7 +2202,7 @@
         <v>500</v>
       </c>
       <c r="C11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
@@ -2216,7 +2219,7 @@
         <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
@@ -2284,7 +2287,7 @@
         <v>500</v>
       </c>
       <c r="C16" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
@@ -2301,7 +2304,7 @@
         <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
@@ -2318,7 +2321,7 @@
         <v>200</v>
       </c>
       <c r="C18" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
@@ -2335,7 +2338,7 @@
         <v>300</v>
       </c>
       <c r="C19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
@@ -2352,7 +2355,7 @@
         <v>400</v>
       </c>
       <c r="C20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -2369,7 +2372,7 @@
         <v>500</v>
       </c>
       <c r="C21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D21" t="n">
         <v>4</v>
@@ -2386,7 +2389,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -2395,7 +2398,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23">
@@ -2406,7 +2409,7 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -2415,7 +2418,7 @@
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="24">
@@ -2426,7 +2429,7 @@
         <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -2435,7 +2438,7 @@
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25">
@@ -2446,7 +2449,7 @@
         <v>110</v>
       </c>
       <c r="C25" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
@@ -2455,7 +2458,7 @@
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26">
@@ -2466,7 +2469,7 @@
         <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -2475,7 +2478,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27">
@@ -2486,7 +2489,7 @@
         <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D27" t="n">
         <v>2</v>
@@ -2495,7 +2498,7 @@
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="28">
@@ -2506,7 +2509,7 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
@@ -2515,7 +2518,7 @@
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29">
@@ -2526,7 +2529,7 @@
         <v>80</v>
       </c>
       <c r="C29" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
@@ -2535,7 +2538,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="30">
@@ -2546,7 +2549,7 @@
         <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D30" t="n">
         <v>2</v>
@@ -2555,7 +2558,7 @@
         <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31">
@@ -2566,7 +2569,7 @@
         <v>150</v>
       </c>
       <c r="C31" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
@@ -2575,7 +2578,7 @@
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="32">
@@ -2586,7 +2589,7 @@
         <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D32" t="n">
         <v>3</v>
@@ -2595,7 +2598,7 @@
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33">
@@ -2606,7 +2609,7 @@
         <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D33" t="n">
         <v>3</v>
@@ -2615,7 +2618,7 @@
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="34">
@@ -2626,7 +2629,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D34" t="n">
         <v>3</v>
@@ -2635,7 +2638,7 @@
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35">
@@ -2646,7 +2649,7 @@
         <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D35" t="n">
         <v>3</v>
@@ -2655,7 +2658,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36">
@@ -2666,7 +2669,7 @@
         <v>150</v>
       </c>
       <c r="C36" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D36" t="n">
         <v>3</v>
@@ -2675,7 +2678,7 @@
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37">
@@ -2686,7 +2689,7 @@
         <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D37" t="n">
         <v>4</v>
@@ -2695,7 +2698,7 @@
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38">
@@ -2706,7 +2709,7 @@
         <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D38" t="n">
         <v>4</v>
@@ -2715,7 +2718,7 @@
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39">
@@ -2726,7 +2729,7 @@
         <v>80</v>
       </c>
       <c r="C39" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D39" t="n">
         <v>4</v>
@@ -2735,7 +2738,7 @@
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="40">
@@ -2746,7 +2749,7 @@
         <v>110</v>
       </c>
       <c r="C40" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D40" t="n">
         <v>4</v>
@@ -2755,7 +2758,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="41">
@@ -2766,7 +2769,7 @@
         <v>150</v>
       </c>
       <c r="C41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D41" t="n">
         <v>4</v>
@@ -2775,7 +2778,7 @@
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -2820,13 +2823,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F2" t="n">
         <v>62001</v>
@@ -2840,13 +2843,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F3" t="n">
         <v>62002</v>
@@ -2860,13 +2863,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F4" t="n">
         <v>62003</v>
@@ -2880,13 +2883,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F5" t="n">
         <v>62004</v>
